--- a/data/trans_orig/P6606-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P6606-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>243850</t>
+          <t>242595</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>278979</t>
+          <t>278504</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>168606</t>
+          <t>169641</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>189734</t>
+          <t>190901</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>424276</t>
+          <t>421963</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>462906</t>
+          <t>461657</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>80,59%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50362</t>
+          <t>49501</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>80036</t>
+          <t>78257</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14471</t>
+          <t>14169</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31973</t>
+          <t>31614</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>69435</t>
+          <t>69868</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>102861</t>
+          <t>104600</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,26%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15512</t>
+          <t>15384</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34449</t>
+          <t>35392</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2065</t>
+          <t>2572</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12856</t>
+          <t>13141</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20208</t>
+          <t>20764</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>44178</t>
+          <t>42006</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4653</t>
+          <t>3976</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16531</t>
+          <t>16328</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10995</t>
+          <t>12399</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7677</t>
+          <t>8391</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23226</t>
+          <t>23556</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>198860</t>
+          <t>198540</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>226214</t>
+          <t>227603</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>210774</t>
+          <t>209974</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>225193</t>
+          <t>224355</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>415828</t>
+          <t>416476</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>447624</t>
+          <t>447891</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,25%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20850</t>
+          <t>20470</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42901</t>
+          <t>43550</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15134</t>
+          <t>15089</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27527</t>
+          <t>27251</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52858</t>
+          <t>53213</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14055</t>
+          <t>13080</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32748</t>
+          <t>31431</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>956</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8392</t>
+          <t>9409</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16006</t>
+          <t>15777</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>37201</t>
+          <t>34955</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>892</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8989</t>
+          <t>7689</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7094</t>
+          <t>5902</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1745</t>
+          <t>1767</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9783</t>
+          <t>10292</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>120166</t>
+          <t>119949</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>159658</t>
+          <t>158209</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>35089</t>
+          <t>35658</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>49050</t>
+          <t>49278</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,75%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>161642</t>
+          <t>161897</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>202530</t>
+          <t>205101</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,94%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>93243</t>
+          <t>95686</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>130447</t>
+          <t>130921</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6094</t>
+          <t>6080</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>18970</t>
+          <t>19703</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>106403</t>
+          <t>105127</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>143639</t>
+          <t>143052</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,74%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>86222</t>
+          <t>85737</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>123094</t>
+          <t>120037</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>945</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7854</t>
+          <t>8848</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>89193</t>
+          <t>89671</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>124565</t>
+          <t>125735</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,78%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15899</t>
+          <t>16427</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36012</t>
+          <t>36699</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16489</t>
+          <t>16033</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>36931</t>
+          <t>35531</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>219591</t>
+          <t>219540</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>271157</t>
+          <t>268885</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>180847</t>
+          <t>180929</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>215451</t>
+          <t>215452</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>411251</t>
+          <t>413581</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>475926</t>
+          <t>477055</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>47,03%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>164872</t>
+          <t>165870</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>214026</t>
+          <t>214439</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>63891</t>
+          <t>63513</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>95644</t>
+          <t>94295</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>240738</t>
+          <t>240978</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>297564</t>
+          <t>296295</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,21%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>181742</t>
+          <t>182370</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>228765</t>
+          <t>230488</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>10744</t>
+          <t>10757</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>26955</t>
+          <t>25676</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>194649</t>
+          <t>196466</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>249393</t>
+          <t>250804</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,72%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>54068</t>
+          <t>56336</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>86383</t>
+          <t>88172</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5409</t>
+          <t>5480</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18349</t>
+          <t>18531</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>64677</t>
+          <t>64839</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>100764</t>
+          <t>100679</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>58446</t>
+          <t>59134</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>86372</t>
+          <t>86729</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>147855</t>
+          <t>147320</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>173230</t>
+          <t>172603</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>211147</t>
+          <t>215366</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>253040</t>
+          <t>254781</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>64,28%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>29296</t>
+          <t>29139</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>51755</t>
+          <t>54270</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>26983</t>
+          <t>27312</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>49747</t>
+          <t>50196</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>62428</t>
+          <t>63253</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>94959</t>
+          <t>95604</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,12%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>41410</t>
+          <t>40874</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>66529</t>
+          <t>66287</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5085</t>
+          <t>4876</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>17969</t>
+          <t>18267</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>47779</t>
+          <t>49798</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>80594</t>
+          <t>80235</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,24%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>12443</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>29253</t>
+          <t>28648</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>977</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>9499</t>
+          <t>10054</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>14710</t>
+          <t>14373</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>33063</t>
+          <t>32848</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -3578,12 +3578,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>889878</t>
+          <t>889365</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>978053</t>
+          <t>975305</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>777345</t>
+          <t>773445</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>828077</t>
+          <t>827451</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3628,12 +3628,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1679957</t>
+          <t>1680218</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1790098</t>
+          <t>1794436</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3663,12 +3663,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>61,4%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>396152</t>
+          <t>398894</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>470570</t>
+          <t>474187</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>137338</t>
+          <t>136324</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>184283</t>
+          <t>184846</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>546948</t>
+          <t>546173</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>638911</t>
+          <t>636892</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,79%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>371667</t>
+          <t>372950</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>446456</t>
+          <t>444140</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>28434</t>
+          <t>28532</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>54215</t>
+          <t>53796</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>409114</t>
+          <t>407886</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>487095</t>
+          <t>487160</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>104871</t>
+          <t>103153</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>149883</t>
+          <t>147054</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>13415</t>
+          <t>13732</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>32926</t>
+          <t>32010</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>125967</t>
+          <t>122974</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>170886</t>
+          <t>169737</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -4380,12 +4380,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>158104</t>
+          <t>158411</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>194072</t>
+          <t>196196</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>137722</t>
+          <t>137347</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>162394</t>
+          <t>162412</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>305612</t>
+          <t>305062</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>349374</t>
+          <t>348564</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>70,1%</t>
         </is>
       </c>
     </row>
@@ -4493,12 +4493,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69162</t>
+          <t>68520</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>103801</t>
+          <t>102885</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4528,12 +4528,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26467</t>
+          <t>27066</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49605</t>
+          <t>50357</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>104306</t>
+          <t>103111</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>144989</t>
+          <t>144409</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,04%</t>
         </is>
       </c>
     </row>
@@ -4606,12 +4606,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25269</t>
+          <t>24355</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>50549</t>
+          <t>48419</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>1811</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11900</t>
+          <t>13095</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4656,12 +4656,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>28533</t>
+          <t>28623</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>54619</t>
+          <t>53946</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -4719,12 +4719,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11479</t>
+          <t>11792</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4734,12 +4734,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5376</t>
+          <t>6858</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2958</t>
+          <t>2874</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13510</t>
+          <t>13412</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4804,12 +4804,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -4949,12 +4949,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>132775</t>
+          <t>133450</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>166665</t>
+          <t>166589</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>134850</t>
+          <t>135606</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>154054</t>
+          <t>154180</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4999,12 +4999,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>274384</t>
+          <t>274507</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>314619</t>
+          <t>316340</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>75,1%</t>
         </is>
       </c>
     </row>
@@ -5062,12 +5062,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>60241</t>
+          <t>60937</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>90618</t>
+          <t>91946</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5077,12 +5077,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7855</t>
+          <t>6987</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24683</t>
+          <t>23811</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5112,12 +5112,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>74761</t>
+          <t>72484</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>109853</t>
+          <t>109347</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5147,12 +5147,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,96%</t>
         </is>
       </c>
     </row>
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16193</t>
+          <t>15496</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36328</t>
+          <t>36778</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>2391</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12409</t>
+          <t>13483</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5225,12 +5225,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>20747</t>
+          <t>20135</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>42821</t>
+          <t>43716</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5260,12 +5260,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -5288,12 +5288,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>981</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9005</t>
+          <t>9862</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5303,12 +5303,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4789</t>
+          <t>4798</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1856</t>
+          <t>1904</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10444</t>
+          <t>10524</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -5518,12 +5518,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>50532</t>
+          <t>50412</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>79612</t>
+          <t>77748</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5533,12 +5533,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>37708</t>
+          <t>38058</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>59710</t>
+          <t>58163</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5568,12 +5568,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>94510</t>
+          <t>93826</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>130272</t>
+          <t>130295</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5603,12 +5603,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,28%</t>
         </is>
       </c>
     </row>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>81449</t>
+          <t>81775</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>111995</t>
+          <t>113948</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5646,12 +5646,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5666,12 +5666,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>31419</t>
+          <t>30578</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>52126</t>
+          <t>51297</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5681,12 +5681,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5701,12 +5701,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>119447</t>
+          <t>119920</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>156419</t>
+          <t>156349</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>39,93%</t>
         </is>
       </c>
     </row>
@@ -5744,12 +5744,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>71809</t>
+          <t>72489</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>103794</t>
+          <t>103732</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5759,12 +5759,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5779,12 +5779,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10480</t>
+          <t>10683</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26175</t>
+          <t>26006</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5794,12 +5794,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5814,12 +5814,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>89057</t>
+          <t>88124</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>123928</t>
+          <t>122892</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5829,12 +5829,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,39%</t>
         </is>
       </c>
     </row>
@@ -5857,12 +5857,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21000</t>
+          <t>21229</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>44759</t>
+          <t>44762</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5872,7 +5872,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>1954</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10808</t>
+          <t>10721</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5927,12 +5927,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25856</t>
+          <t>25953</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>50103</t>
+          <t>49519</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5942,12 +5942,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,65%</t>
         </is>
       </c>
     </row>
@@ -6087,12 +6087,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>87732</t>
+          <t>87420</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>122696</t>
+          <t>125552</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6102,12 +6102,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6122,12 +6122,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>85270</t>
+          <t>84780</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>118407</t>
+          <t>117989</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6137,12 +6137,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6157,12 +6157,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>182466</t>
+          <t>181902</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>231554</t>
+          <t>233367</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6172,12 +6172,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,33%</t>
         </is>
       </c>
     </row>
@@ -6200,12 +6200,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>112738</t>
+          <t>114871</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>152610</t>
+          <t>153140</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6215,12 +6215,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6235,12 +6235,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>102922</t>
+          <t>105152</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>136630</t>
+          <t>138549</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6250,12 +6250,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6270,12 +6270,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>223742</t>
+          <t>225976</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>281437</t>
+          <t>280399</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6285,12 +6285,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>38,84%</t>
         </is>
       </c>
     </row>
@@ -6313,12 +6313,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>95339</t>
+          <t>95452</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>133395</t>
+          <t>131505</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6328,12 +6328,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6348,12 +6348,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>41433</t>
+          <t>40228</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>68015</t>
+          <t>67256</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6363,12 +6363,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6383,12 +6383,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>144228</t>
+          <t>144885</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>190909</t>
+          <t>192203</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6398,12 +6398,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,62%</t>
         </is>
       </c>
     </row>
@@ -6426,12 +6426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>55704</t>
+          <t>57134</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>88928</t>
+          <t>89078</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6441,12 +6441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6461,12 +6461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14124</t>
+          <t>14191</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32444</t>
+          <t>32679</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6496,12 +6496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>76835</t>
+          <t>76992</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>114170</t>
+          <t>113937</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,78%</t>
         </is>
       </c>
     </row>
@@ -6656,12 +6656,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10413</t>
+          <t>10351</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>25836</t>
+          <t>25094</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6671,12 +6671,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>54117</t>
+          <t>54018</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>80808</t>
+          <t>81535</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>67041</t>
+          <t>68136</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>100027</t>
+          <t>100182</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,49%</t>
         </is>
       </c>
     </row>
@@ -6769,12 +6769,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22621</t>
+          <t>22295</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>43509</t>
+          <t>43108</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6784,12 +6784,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6804,12 +6804,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>55177</t>
+          <t>53686</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>80391</t>
+          <t>81666</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>83328</t>
+          <t>83547</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>116213</t>
+          <t>118151</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,96%</t>
         </is>
       </c>
     </row>
@@ -6882,12 +6882,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>41103</t>
+          <t>40916</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>64350</t>
+          <t>64615</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6897,12 +6897,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>15294</t>
+          <t>15978</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>33557</t>
+          <t>34634</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>62585</t>
+          <t>60597</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>93120</t>
+          <t>91467</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>27,84%</t>
         </is>
       </c>
     </row>
@@ -6995,12 +6995,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>39986</t>
+          <t>41105</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>64341</t>
+          <t>64520</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7010,12 +7010,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>10214</t>
+          <t>9580</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>27726</t>
+          <t>27545</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>55149</t>
+          <t>55728</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>87063</t>
+          <t>88028</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,8%</t>
         </is>
       </c>
     </row>
@@ -7225,12 +7225,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>474348</t>
+          <t>475784</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>549930</t>
+          <t>554129</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7240,12 +7240,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7260,12 +7260,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>481517</t>
+          <t>479213</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>547024</t>
+          <t>545318</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>975415</t>
+          <t>974479</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1077484</t>
+          <t>1076928</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>45,62%</t>
         </is>
       </c>
     </row>
@@ -7338,12 +7338,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>389936</t>
+          <t>384545</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>462171</t>
+          <t>459027</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7353,12 +7353,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7373,12 +7373,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>252825</t>
+          <t>252301</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>310386</t>
+          <t>312696</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>660369</t>
+          <t>660055</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>753764</t>
+          <t>751578</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,84%</t>
         </is>
       </c>
     </row>
@@ -7451,12 +7451,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>281715</t>
+          <t>280762</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>344816</t>
+          <t>345392</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7466,12 +7466,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7486,12 +7486,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>87893</t>
+          <t>87648</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>127998</t>
+          <t>127645</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7521,12 +7521,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>383871</t>
+          <t>381533</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>458744</t>
+          <t>456818</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,35%</t>
         </is>
       </c>
     </row>
@@ -7564,12 +7564,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>142571</t>
+          <t>142322</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>192032</t>
+          <t>189696</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7579,12 +7579,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7599,12 +7599,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>34877</t>
+          <t>34785</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>61798</t>
+          <t>64917</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7634,12 +7634,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>183827</t>
+          <t>185398</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>238691</t>
+          <t>242974</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -8027,12 +8027,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>183276</t>
+          <t>184481</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>213698</t>
+          <t>214517</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8042,12 +8042,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>148896</t>
+          <t>149668</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>173623</t>
+          <t>175616</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>341595</t>
+          <t>341701</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>383065</t>
+          <t>382436</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8112,12 +8112,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,65%</t>
         </is>
       </c>
     </row>
@@ -8140,12 +8140,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32406</t>
+          <t>32458</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57854</t>
+          <t>55820</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8155,12 +8155,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26599</t>
+          <t>25992</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47699</t>
+          <t>48719</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>63427</t>
+          <t>64239</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>96671</t>
+          <t>97593</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8225,12 +8225,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,82%</t>
         </is>
       </c>
     </row>
@@ -8253,12 +8253,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17930</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>39923</t>
+          <t>39376</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8268,12 +8268,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>7024</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21568</t>
+          <t>20974</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8303,12 +8303,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>29557</t>
+          <t>29516</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>54548</t>
+          <t>54896</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8338,12 +8338,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -8366,12 +8366,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3397</t>
+          <t>3018</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15728</t>
+          <t>15434</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8381,12 +8381,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7088</t>
+          <t>7131</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4897</t>
+          <t>4939</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17054</t>
+          <t>18564</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8451,12 +8451,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -8596,12 +8596,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>147841</t>
+          <t>147252</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>179011</t>
+          <t>177578</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8611,12 +8611,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>136555</t>
+          <t>136818</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>160013</t>
+          <t>158687</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8646,12 +8646,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>290875</t>
+          <t>290699</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>329082</t>
+          <t>327571</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8681,12 +8681,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>76,26%</t>
         </is>
       </c>
     </row>
@@ -8709,12 +8709,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34269</t>
+          <t>33246</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60300</t>
+          <t>59506</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8724,12 +8724,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20538</t>
+          <t>21325</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41311</t>
+          <t>41235</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8759,12 +8759,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>60898</t>
+          <t>61132</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>92679</t>
+          <t>94416</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8794,12 +8794,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,98%</t>
         </is>
       </c>
     </row>
@@ -8822,12 +8822,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16003</t>
+          <t>15781</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35715</t>
+          <t>36597</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8837,12 +8837,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5546</t>
+          <t>5558</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19403</t>
+          <t>18885</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8872,12 +8872,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>25534</t>
+          <t>25990</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>48029</t>
+          <t>48816</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8907,12 +8907,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,36%</t>
         </is>
       </c>
     </row>
@@ -8935,12 +8935,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2923</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13646</t>
+          <t>13803</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8950,12 +8950,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5802</t>
+          <t>5517</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8990,7 +8990,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3872</t>
+          <t>3136</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>14332</t>
+          <t>15970</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9020,12 +9020,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -9165,12 +9165,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>43422</t>
+          <t>44696</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>70527</t>
+          <t>71227</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9180,12 +9180,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>32674</t>
+          <t>32425</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>48331</t>
+          <t>48245</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9215,12 +9215,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>80173</t>
+          <t>81181</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>112512</t>
+          <t>114311</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9250,12 +9250,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>40,7%</t>
         </is>
       </c>
     </row>
@@ -9278,12 +9278,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>61726</t>
+          <t>62813</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>90846</t>
+          <t>91674</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9293,12 +9293,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11663</t>
+          <t>11174</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>25505</t>
+          <t>26505</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9328,12 +9328,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>79270</t>
+          <t>78126</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>112357</t>
+          <t>110017</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9363,12 +9363,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>39,17%</t>
         </is>
       </c>
     </row>
@@ -9391,12 +9391,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>47314</t>
+          <t>47885</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>73090</t>
+          <t>73185</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9406,12 +9406,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2815</t>
+          <t>2841</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12608</t>
+          <t>13054</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9441,12 +9441,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52937</t>
+          <t>53112</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>81388</t>
+          <t>82931</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9476,12 +9476,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,52%</t>
         </is>
       </c>
     </row>
@@ -9504,12 +9504,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12495</t>
+          <t>13434</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30271</t>
+          <t>30836</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9519,12 +9519,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5684</t>
+          <t>6624</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9559,7 +9559,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14098</t>
+          <t>14264</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32883</t>
+          <t>32272</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9589,12 +9589,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,49%</t>
         </is>
       </c>
     </row>
@@ -9734,12 +9734,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>104676</t>
+          <t>102920</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>142787</t>
+          <t>143075</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9749,12 +9749,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>120250</t>
+          <t>120072</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>158223</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9784,12 +9784,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>234864</t>
+          <t>235954</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>288703</t>
+          <t>291534</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9819,12 +9819,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>34,32%</t>
         </is>
       </c>
     </row>
@@ -9847,12 +9847,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>150071</t>
+          <t>152969</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>191818</t>
+          <t>194933</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9862,12 +9862,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>99225</t>
+          <t>99207</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>134747</t>
+          <t>135335</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9897,12 +9897,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>260389</t>
+          <t>262947</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>316096</t>
+          <t>315696</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9932,12 +9932,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,16%</t>
         </is>
       </c>
     </row>
@@ -9960,12 +9960,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>98014</t>
+          <t>98990</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>136653</t>
+          <t>136073</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9975,12 +9975,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>62166</t>
+          <t>62025</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>93926</t>
+          <t>92830</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10010,12 +10010,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>170576</t>
+          <t>169667</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>219517</t>
+          <t>218568</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,73%</t>
         </is>
       </c>
     </row>
@@ -10073,12 +10073,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>55131</t>
+          <t>54555</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>87322</t>
+          <t>86498</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10088,12 +10088,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26766</t>
+          <t>26675</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>50122</t>
+          <t>49928</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>88255</t>
+          <t>87758</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>127535</t>
+          <t>126175</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,85%</t>
         </is>
       </c>
     </row>
@@ -10303,12 +10303,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>15063</t>
+          <t>14291</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>33609</t>
+          <t>33767</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>61114</t>
+          <t>61578</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>88103</t>
+          <t>88122</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10353,12 +10353,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>80003</t>
+          <t>80817</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>114142</t>
+          <t>116296</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,77%</t>
         </is>
       </c>
     </row>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>43737</t>
+          <t>42501</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>69925</t>
+          <t>68589</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10431,12 +10431,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>63258</t>
+          <t>64530</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>90840</t>
+          <t>91459</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10466,12 +10466,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>115044</t>
+          <t>115019</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>153495</t>
+          <t>152626</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10506,7 +10506,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,08%</t>
         </is>
       </c>
     </row>
@@ -10529,12 +10529,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>46821</t>
+          <t>45972</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>72916</t>
+          <t>72663</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10544,12 +10544,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>18061</t>
+          <t>17538</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>37305</t>
+          <t>36239</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10579,12 +10579,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>68738</t>
+          <t>68614</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>103291</t>
+          <t>102303</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10614,12 +10614,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,19%</t>
         </is>
       </c>
     </row>
@@ -10642,12 +10642,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>42868</t>
+          <t>45223</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>71204</t>
+          <t>70118</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10657,12 +10657,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -10677,12 +10677,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>11130</t>
+          <t>12039</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>29304</t>
+          <t>27847</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10692,12 +10692,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -10712,12 +10712,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>59252</t>
+          <t>58740</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>91280</t>
+          <t>92264</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10727,12 +10727,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,62%</t>
         </is>
       </c>
     </row>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>529153</t>
+          <t>526315</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>600903</t>
+          <t>601713</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10887,12 +10887,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>531312</t>
+          <t>533164</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>594696</t>
+          <t>598222</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10922,12 +10922,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1080274</t>
+          <t>1079928</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1175229</t>
+          <t>1178318</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10957,12 +10957,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>48,23%</t>
         </is>
       </c>
     </row>
@@ -10985,12 +10985,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>361897</t>
+          <t>357326</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>433060</t>
+          <t>430197</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11000,12 +11000,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>250339</t>
+          <t>251225</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>304581</t>
+          <t>305331</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>627810</t>
+          <t>630456</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>718801</t>
+          <t>717626</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11070,12 +11070,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,37%</t>
         </is>
       </c>
     </row>
@@ -11098,12 +11098,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>257150</t>
+          <t>257952</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>317813</t>
+          <t>319727</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11113,12 +11113,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>112842</t>
+          <t>114511</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>156110</t>
+          <t>154766</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11148,12 +11148,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>384538</t>
+          <t>385418</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>457273</t>
+          <t>458040</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11183,12 +11183,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,75%</t>
         </is>
       </c>
     </row>
@@ -11211,12 +11211,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>135920</t>
+          <t>137518</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>187152</t>
+          <t>187080</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>45934</t>
+          <t>46585</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>77290</t>
+          <t>77946</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11261,12 +11261,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>192162</t>
+          <t>190327</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>249256</t>
+          <t>248681</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11296,12 +11296,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -11669,32 +11669,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>141728</t>
+          <t>156350</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>128842</t>
+          <t>141957</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>152140</t>
+          <t>167719</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11704,32 +11704,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>120595</t>
+          <t>129866</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>111225</t>
+          <t>119229</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>127109</t>
+          <t>136970</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11739,32 +11739,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>262323</t>
+          <t>286216</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>246553</t>
+          <t>270612</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>276077</t>
+          <t>301840</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,62%</t>
         </is>
       </c>
     </row>
@@ -11782,32 +11782,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25909</t>
+          <t>27929</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16984</t>
+          <t>19378</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36093</t>
+          <t>40291</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11817,32 +11817,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21433</t>
+          <t>22009</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15181</t>
+          <t>15585</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29253</t>
+          <t>31343</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11852,32 +11852,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>47342</t>
+          <t>49938</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34949</t>
+          <t>37216</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>60058</t>
+          <t>62350</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>17,27%</t>
         </is>
       </c>
     </row>
@@ -11895,32 +11895,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8193</t>
+          <t>11677</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3944</t>
+          <t>5354</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14516</t>
+          <t>22135</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11930,32 +11930,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4470</t>
+          <t>4842</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1904</t>
+          <t>2205</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8912</t>
+          <t>10404</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11965,32 +11965,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>12663</t>
+          <t>16519</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7305</t>
+          <t>10092</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20158</t>
+          <t>27520</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -12008,32 +12008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4027</t>
+          <t>4011</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>976</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10813</t>
+          <t>13371</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12043,32 +12043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4119</t>
+          <t>4291</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1391</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8260</t>
+          <t>9442</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12078,32 +12078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>8145</t>
+          <t>8303</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>3828</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16199</t>
+          <t>17627</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -12121,17 +12121,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>179857</t>
+          <t>199967</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>179857</t>
+          <t>199967</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>179857</t>
+          <t>199967</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12156,17 +12156,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>150617</t>
+          <t>161008</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>150617</t>
+          <t>161008</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>150617</t>
+          <t>161008</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12191,17 +12191,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>330474</t>
+          <t>360976</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>330474</t>
+          <t>360976</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>330474</t>
+          <t>360976</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12238,32 +12238,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>114463</t>
+          <t>118913</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>101463</t>
+          <t>104733</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>125707</t>
+          <t>130015</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12273,17 +12273,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>93587</t>
+          <t>100654</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>86038</t>
+          <t>91594</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>100487</t>
+          <t>108799</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -12293,12 +12293,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -12308,32 +12308,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>208051</t>
+          <t>219567</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>191598</t>
+          <t>203217</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>222607</t>
+          <t>234313</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,38%</t>
         </is>
       </c>
     </row>
@@ -12351,32 +12351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>28952</t>
+          <t>30582</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19439</t>
+          <t>21126</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40777</t>
+          <t>43068</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12386,32 +12386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>14307</t>
+          <t>15092</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8823</t>
+          <t>9298</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21304</t>
+          <t>23524</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12421,32 +12421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>43259</t>
+          <t>45674</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31276</t>
+          <t>33122</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56655</t>
+          <t>59558</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,43%</t>
         </is>
       </c>
     </row>
@@ -12464,32 +12464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11815</t>
+          <t>11979</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6218</t>
+          <t>6126</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19924</t>
+          <t>20354</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12499,32 +12499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3814</t>
+          <t>4577</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7682</t>
+          <t>9807</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12534,22 +12534,22 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>15629</t>
+          <t>16556</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9475</t>
+          <t>10007</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>25049</t>
+          <t>25662</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -12559,7 +12559,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,8%</t>
         </is>
       </c>
     </row>
@@ -12577,32 +12577,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4829</t>
+          <t>5410</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>956</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15036</t>
+          <t>16635</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12612,32 +12612,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4152</t>
+          <t>4287</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1192</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10954</t>
+          <t>11105</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12647,32 +12647,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>8982</t>
+          <t>9697</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>4218</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19143</t>
+          <t>22835</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -12690,17 +12690,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>160060</t>
+          <t>166884</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>160060</t>
+          <t>166884</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>160060</t>
+          <t>166884</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12725,17 +12725,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>115860</t>
+          <t>124610</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>115860</t>
+          <t>124610</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>115860</t>
+          <t>124610</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12760,17 +12760,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>275920</t>
+          <t>291494</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>275920</t>
+          <t>291494</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>275920</t>
+          <t>291494</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12807,32 +12807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>271603</t>
+          <t>28953</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>71726</t>
+          <t>19271</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>344469</t>
+          <t>40140</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12842,32 +12842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>24569</t>
+          <t>27836</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18584</t>
+          <t>21714</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30209</t>
+          <t>34294</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12877,32 +12877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>296172</t>
+          <t>56789</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>115828</t>
+          <t>44444</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>381798</t>
+          <t>72570</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>37,84%</t>
         </is>
       </c>
     </row>
@@ -12920,32 +12920,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>36920</t>
+          <t>39104</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9998</t>
+          <t>29263</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>118441</t>
+          <t>52093</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -12955,32 +12955,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14866</t>
+          <t>16414</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9943</t>
+          <t>11060</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>20647</t>
+          <t>22053</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -12990,32 +12990,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>51786</t>
+          <t>55518</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>15325</t>
+          <t>42744</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>133425</t>
+          <t>70924</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>36,98%</t>
         </is>
       </c>
     </row>
@@ -13033,32 +13033,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>45330</t>
+          <t>50402</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12455</t>
+          <t>38608</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>140024</t>
+          <t>63412</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13068,32 +13068,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5410</t>
+          <t>5446</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2293</t>
+          <t>2208</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10100</t>
+          <t>9724</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13103,32 +13103,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>50740</t>
+          <t>55848</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12956</t>
+          <t>41931</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>130211</t>
+          <t>69225</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>36,1%</t>
         </is>
       </c>
     </row>
@@ -13146,32 +13146,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18541</t>
+          <t>23629</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3864</t>
+          <t>13743</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>61809</t>
+          <t>36167</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13216,32 +13216,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>18541</t>
+          <t>23629</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4220</t>
+          <t>13957</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51132</t>
+          <t>37948</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>19,79%</t>
         </is>
       </c>
     </row>
@@ -13259,17 +13259,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>372394</t>
+          <t>142088</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>372394</t>
+          <t>142088</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>372394</t>
+          <t>142088</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13294,17 +13294,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>44845</t>
+          <t>49696</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>44845</t>
+          <t>49696</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>44845</t>
+          <t>49696</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13329,17 +13329,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>417239</t>
+          <t>191784</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>417239</t>
+          <t>191784</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>417239</t>
+          <t>191784</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13376,32 +13376,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>57628</t>
+          <t>64741</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>43552</t>
+          <t>49945</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>74196</t>
+          <t>82197</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13411,32 +13411,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>56845</t>
+          <t>66320</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>46299</t>
+          <t>53882</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>68624</t>
+          <t>79559</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13446,32 +13446,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>114474</t>
+          <t>131061</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>96619</t>
+          <t>111843</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>135299</t>
+          <t>153270</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,94%</t>
         </is>
       </c>
     </row>
@@ -13489,32 +13489,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>90881</t>
+          <t>100421</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>74285</t>
+          <t>84804</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>107871</t>
+          <t>119422</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13524,32 +13524,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>75802</t>
+          <t>83466</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>64259</t>
+          <t>70541</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>88801</t>
+          <t>96253</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13559,32 +13559,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>166683</t>
+          <t>183886</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>147895</t>
+          <t>160868</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>189071</t>
+          <t>205263</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>40,09%</t>
         </is>
       </c>
     </row>
@@ -13602,32 +13602,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>79452</t>
+          <t>88464</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>64196</t>
+          <t>70284</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>96327</t>
+          <t>106169</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -13637,32 +13637,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>39377</t>
+          <t>42974</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>30054</t>
+          <t>33732</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>49857</t>
+          <t>53797</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13672,32 +13672,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>118829</t>
+          <t>131438</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>99240</t>
+          <t>110285</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>138146</t>
+          <t>151862</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>29,66%</t>
         </is>
       </c>
     </row>
@@ -13715,32 +13715,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>30693</t>
+          <t>36448</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21319</t>
+          <t>25651</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>43222</t>
+          <t>51280</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13750,32 +13750,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>26503</t>
+          <t>29168</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18956</t>
+          <t>21061</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>36660</t>
+          <t>39587</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13785,32 +13785,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>57196</t>
+          <t>65616</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>43661</t>
+          <t>51811</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>73829</t>
+          <t>81060</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,83%</t>
         </is>
       </c>
     </row>
@@ -13828,17 +13828,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>258655</t>
+          <t>290074</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>258655</t>
+          <t>290074</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>258655</t>
+          <t>290074</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13863,17 +13863,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>198527</t>
+          <t>221928</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>198527</t>
+          <t>221928</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>198527</t>
+          <t>221928</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13898,17 +13898,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>457182</t>
+          <t>512002</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>457182</t>
+          <t>512002</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>457182</t>
+          <t>512002</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13945,32 +13945,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>18881</t>
+          <t>23403</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10928</t>
+          <t>14823</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>29960</t>
+          <t>34331</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13980,32 +13980,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>30998</t>
+          <t>34936</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14981</t>
+          <t>26949</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>42508</t>
+          <t>45553</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14015,32 +14015,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>49879</t>
+          <t>58338</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>34719</t>
+          <t>47032</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>64556</t>
+          <t>73632</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>22,77%</t>
         </is>
       </c>
     </row>
@@ -14058,32 +14058,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>35480</t>
+          <t>42288</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25013</t>
+          <t>30183</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>49827</t>
+          <t>58632</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14093,32 +14093,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>87998</t>
+          <t>68390</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>64843</t>
+          <t>56981</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>121978</t>
+          <t>79613</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14128,32 +14128,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>123478</t>
+          <t>110678</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>93227</t>
+          <t>95522</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>173081</t>
+          <t>131193</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>40,57%</t>
         </is>
       </c>
     </row>
@@ -14171,32 +14171,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>37537</t>
+          <t>48047</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>26058</t>
+          <t>34192</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>50749</t>
+          <t>62564</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14206,32 +14206,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>28120</t>
+          <t>33207</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>13799</t>
+          <t>25276</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>40120</t>
+          <t>43919</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14241,32 +14241,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>65656</t>
+          <t>81253</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>41891</t>
+          <t>66108</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>81718</t>
+          <t>97990</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>30,3%</t>
         </is>
       </c>
     </row>
@@ -14284,32 +14284,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>40376</t>
+          <t>55013</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>28243</t>
+          <t>41017</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>52627</t>
+          <t>70321</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -14319,32 +14319,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>15734</t>
+          <t>18087</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>7051</t>
+          <t>11985</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>24925</t>
+          <t>27448</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -14354,32 +14354,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>56109</t>
+          <t>73100</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>37340</t>
+          <t>56503</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>75740</t>
+          <t>92366</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>28,56%</t>
         </is>
       </c>
     </row>
@@ -14397,17 +14397,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>132274</t>
+          <t>168750</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>132274</t>
+          <t>168750</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>132274</t>
+          <t>168750</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14432,17 +14432,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>162849</t>
+          <t>154620</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>162849</t>
+          <t>154620</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>162849</t>
+          <t>154620</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14467,17 +14467,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>295123</t>
+          <t>323369</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>295123</t>
+          <t>323369</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>295123</t>
+          <t>323369</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14514,32 +14514,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>604304</t>
+          <t>392361</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>450194</t>
+          <t>359580</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>840565</t>
+          <t>426013</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14549,32 +14549,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>326596</t>
+          <t>359612</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>265747</t>
+          <t>336813</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>353792</t>
+          <t>383949</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14584,32 +14584,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>930899</t>
+          <t>751973</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>778032</t>
+          <t>708936</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1267011</t>
+          <t>791454</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>47,12%</t>
         </is>
       </c>
     </row>
@@ -14627,32 +14627,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>218144</t>
+          <t>240322</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>110772</t>
+          <t>211120</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>292324</t>
+          <t>269788</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14662,32 +14662,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>214406</t>
+          <t>205371</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>182863</t>
+          <t>182964</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>313083</t>
+          <t>225571</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14697,32 +14697,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>432549</t>
+          <t>445693</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>251403</t>
+          <t>411649</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>529327</t>
+          <t>483860</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>28,81%</t>
         </is>
       </c>
     </row>
@@ -14740,32 +14740,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>182327</t>
+          <t>210569</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>95428</t>
+          <t>184644</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>247208</t>
+          <t>241603</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14775,32 +14775,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>81190</t>
+          <t>91045</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>65059</t>
+          <t>75923</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>98512</t>
+          <t>107058</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14810,32 +14810,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>263517</t>
+          <t>301615</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>159378</t>
+          <t>268343</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>317384</t>
+          <t>333717</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>19,87%</t>
         </is>
       </c>
     </row>
@@ -14853,32 +14853,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>98466</t>
+          <t>124511</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>47985</t>
+          <t>101413</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>137588</t>
+          <t>151916</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14888,32 +14888,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>50507</t>
+          <t>55834</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>38214</t>
+          <t>42654</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>65826</t>
+          <t>69381</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14923,32 +14923,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>148973</t>
+          <t>180344</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>94026</t>
+          <t>155058</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>185717</t>
+          <t>211473</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>12,59%</t>
         </is>
       </c>
     </row>
@@ -14966,17 +14966,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1103241</t>
+          <t>967763</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1103241</t>
+          <t>967763</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1103241</t>
+          <t>967763</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -15001,17 +15001,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>672699</t>
+          <t>711862</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>672699</t>
+          <t>711862</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>672699</t>
+          <t>711862</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -15036,17 +15036,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1775939</t>
+          <t>1679625</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1775939</t>
+          <t>1679625</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1775939</t>
+          <t>1679625</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
